--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -504,7 +504,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
@@ -516,14 +516,14 @@
         </is>
       </c>
       <c r="B3" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="4" t="n">
         <v>2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>27</v>
+        <v>33</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>8</v>
@@ -542,16 +542,16 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -576,7 +576,9 @@
       </c>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
+      <c r="D6" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
@@ -589,18 +591,14 @@
       </c>
       <c r="B7" s="3" t="inlineStr"/>
       <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="G7" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>4</v>
+      </c>
+      <c r="G7" s="3" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -523,14 +523,12 @@
         <v>2</v>
       </c>
       <c r="E3" s="4" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>8</v>
-      </c>
-      <c r="G3" s="4" t="n">
-        <v>1</v>
-      </c>
+        <v>10</v>
+      </c>
+      <c r="G3" s="3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -542,13 +540,13 @@
         <v>1</v>
       </c>
       <c r="C4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>3</v>
@@ -576,10 +574,10 @@
       </c>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="4" t="n">
+      <c r="D6" s="3" t="inlineStr"/>
+      <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -593,12 +591,14 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>4</v>
-      </c>
-      <c r="G7" s="3" t="inlineStr"/>
+        <v>2</v>
+      </c>
+      <c r="G7" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -504,7 +504,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
@@ -519,16 +519,16 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="4" t="n">
-        <v>2</v>
-      </c>
+      <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>32</v>
+        <v>27</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" s="3" t="inlineStr"/>
+        <v>6</v>
+      </c>
+      <c r="G3" s="4" t="n">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -536,17 +536,15 @@
           <t>Isolated compromise</t>
         </is>
       </c>
-      <c r="B4" s="4" t="n">
-        <v>1</v>
-      </c>
+      <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="4" t="n">
         <v>4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="F4" s="4" t="n">
         <v>3</v>
@@ -574,10 +572,10 @@
       </c>
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
-      <c r="D6" s="3" t="inlineStr"/>
-      <c r="E6" s="4" t="n">
+      <c r="D6" s="4" t="n">
         <v>1</v>
       </c>
+      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -594,7 +592,7 @@
         <v>6</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -524,7 +524,7 @@
         <v>27</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -521,10 +521,10 @@
       <c r="C3" s="3" t="inlineStr"/>
       <c r="D3" s="3" t="inlineStr"/>
       <c r="E3" s="4" t="n">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="F3" s="4" t="n">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="G3" s="4" t="n">
         <v>1</v>
@@ -541,13 +541,13 @@
         <v>4</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="E4" s="4" t="n">
         <v>24</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -589,10 +589,10 @@
       <c r="C7" s="3" t="inlineStr"/>
       <c r="D7" s="3" t="inlineStr"/>
       <c r="E7" s="4" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="F7" s="4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="G7" s="4" t="n">
         <v>1</v>

--- a/risk_matrix/risk_matrix_2020.xlsx
+++ b/risk_matrix/risk_matrix_2020.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Risk Matrix" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -27,11 +27,11 @@
     </font>
     <font>
       <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="11"/>
     </font>
   </fonts>
   <fills count="3">
@@ -68,10 +68,10 @@
   </cellStyleXfs>
   <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -504,7 +504,7 @@
       <c r="C2" s="3" t="inlineStr"/>
       <c r="D2" s="3" t="inlineStr"/>
       <c r="E2" s="4" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="F2" s="3" t="inlineStr"/>
       <c r="G2" s="3" t="inlineStr"/>
@@ -519,15 +519,17 @@
         <v>3</v>
       </c>
       <c r="C3" s="3" t="inlineStr"/>
-      <c r="D3" s="3" t="inlineStr"/>
+      <c r="D3" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E3" s="4" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="F3" s="4" t="n">
         <v>5</v>
       </c>
       <c r="G3" s="4" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4">
@@ -538,16 +540,16 @@
       </c>
       <c r="B4" s="3" t="inlineStr"/>
       <c r="C4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D4" s="4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="E4" s="4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F4" s="4" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="G4" s="3" t="inlineStr"/>
     </row>
@@ -573,9 +575,11 @@
       <c r="B6" s="3" t="inlineStr"/>
       <c r="C6" s="3" t="inlineStr"/>
       <c r="D6" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="E6" s="4" t="n">
         <v>1</v>
       </c>
-      <c r="E6" s="3" t="inlineStr"/>
       <c r="F6" s="3" t="inlineStr"/>
       <c r="G6" s="3" t="inlineStr"/>
     </row>
@@ -586,16 +590,20 @@
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr"/>
-      <c r="C7" s="3" t="inlineStr"/>
-      <c r="D7" s="3" t="inlineStr"/>
+      <c r="C7" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D7" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="E7" s="4" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="F7" s="4" t="n">
         <v>2</v>
       </c>
       <c r="G7" s="4" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
